--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_level_info[等级信息].xlsx
@@ -1239,7 +1239,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="G7" s="0" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="8">
@@ -1264,7 +1264,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>3</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="G8" s="0" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="9">
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>4</v>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="G9" s="0" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>100000</v>
+        <v>15000</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>4</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="G10" s="0" t="n">
-        <v>100000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="11">
@@ -1339,7 +1339,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>500000</v>
+        <v>21000</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>5</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G11" s="0" t="n">
-        <v>500000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="12">
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>1000000</v>
+        <v>28000</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>5</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="G12" s="0" t="n">
-        <v>1000000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="13">
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>5000000</v>
+        <v>36000</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>6</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="G13" s="0" t="n">
-        <v>5000000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="1">
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>10000000</v>
+        <v>45000</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>6</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="G14" s="0" t="n">
-        <v>10000000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="1"/>
